--- a/business_forms/042_store_locator_search_form--business_forms.xlsx
+++ b/business_forms/042_store_locator_search_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -972,8 +972,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="49" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'retail',_'label':_'retail'}</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Retail', 'label': 'Retail'}</t>
+          <t>Retail</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'service',_'label':_'service'}</t>
+          <t>service</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Service', 'label': 'Service'}</t>
+          <t>Service</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'miles',_'label':_'miles'}</t>
+          <t>miles</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'miles', 'label': 'miles'}</t>
+          <t>miles</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'kilometers',_'label':_'kilometers'}</t>
+          <t>kilometers</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'kilometers', 'label': 'kilometers'}</t>
+          <t>kilometers</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'store',_'label':_'store'}</t>
+          <t>store</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Store', 'label': 'Store'}</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'service_station',_'label':_'service_station'}</t>
+          <t>service_station</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Service Station', 'label': 'Service Station'}</t>
+          <t>Service Station</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1120,12 +1120,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'english',_'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'English', 'label': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'spanish',_'label':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Spanish', 'label': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'french',_'label':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'French', 'label': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'united_states',_'label':_'united_states'}</t>
+          <t>united_states</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'United States', 'label': 'United States'}</t>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'canada',_'label':_'canada'}</t>
+          <t>canada</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Canada', 'label': 'Canada'}</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'alabama',_'label':_'alabama'}</t>
+          <t>alabama</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Alabama', 'label': 'Alabama'}</t>
+          <t>Alabama</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'alaska',_'label':_'alaska'}</t>
+          <t>alaska</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Alaska', 'label': 'Alaska'}</t>
+          <t>Alaska</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'arizona',_'label':_'arizona'}</t>
+          <t>arizona</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Arizona', 'label': 'Arizona'}</t>
+          <t>Arizona</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'arkansas',_'label':_'arkansas'}</t>
+          <t>arkansas</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Arkansas', 'label': 'Arkansas'}</t>
+          <t>Arkansas</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'california',_'label':_'california'}</t>
+          <t>california</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'California', 'label': 'California'}</t>
+          <t>California</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'colorado',_'label':_'colorado'}</t>
+          <t>colorado</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'Colorado', 'label': 'Colorado'}</t>
+          <t>Colorado</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'connecticut',_'label':_'connecticut'}</t>
+          <t>connecticut</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'Connecticut', 'label': 'Connecticut'}</t>
+          <t>Connecticut</t>
         </is>
       </c>
     </row>
@@ -1324,12 +1324,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'delaware',_'label':_'delaware'}</t>
+          <t>delaware</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'Delaware', 'label': 'Delaware'}</t>
+          <t>Delaware</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'district_of_columbia',_'label':_'district_of_columbia'}</t>
+          <t>district_of_columbia</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'District of Columbia', 'label': 'District of Columbia'}</t>
+          <t>District of Columbia</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'florida',_'label':_'florida'}</t>
+          <t>florida</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'Florida', 'label': 'Florida'}</t>
+          <t>Florida</t>
         </is>
       </c>
     </row>
@@ -1375,12 +1375,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'georgia',_'label':_'georgia'}</t>
+          <t>georgia</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'Georgia', 'label': 'Georgia'}</t>
+          <t>Georgia</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'hawaii',_'label':_'hawaii'}</t>
+          <t>hawaii</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'Hawaii', 'label': 'Hawaii'}</t>
+          <t>Hawaii</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'idaho',_'label':_'idaho'}</t>
+          <t>idaho</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'Idaho', 'label': 'Idaho'}</t>
+          <t>Idaho</t>
         </is>
       </c>
     </row>
@@ -1426,12 +1426,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'illinois',_'label':_'illinois'}</t>
+          <t>illinois</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'Illinois', 'label': 'Illinois'}</t>
+          <t>Illinois</t>
         </is>
       </c>
     </row>
@@ -1443,12 +1443,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_15,_'name':_'indiana',_'label':_'indiana'}</t>
+          <t>indiana</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 15, 'name': 'Indiana', 'label': 'Indiana'}</t>
+          <t>Indiana</t>
         </is>
       </c>
     </row>
@@ -1460,12 +1460,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_16,_'name':_'iowa',_'label':_'iowa'}</t>
+          <t>iowa</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 16, 'name': 'Iowa', 'label': 'Iowa'}</t>
+          <t>Iowa</t>
         </is>
       </c>
     </row>
@@ -1477,12 +1477,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_17,_'name':_'kansas',_'label':_'kansas'}</t>
+          <t>kansas</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 17, 'name': 'Kansas', 'label': 'Kansas'}</t>
+          <t>Kansas</t>
         </is>
       </c>
     </row>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_18,_'name':_'kentucky',_'label':_'kentucky'}</t>
+          <t>kentucky</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 18, 'name': 'Kentucky', 'label': 'Kentucky'}</t>
+          <t>Kentucky</t>
         </is>
       </c>
     </row>
@@ -1511,12 +1511,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_19,_'name':_'louisiana',_'label':_'louisiana'}</t>
+          <t>louisiana</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 19, 'name': 'Louisiana', 'label': 'Louisiana'}</t>
+          <t>Louisiana</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_20,_'name':_'maine',_'label':_'maine'}</t>
+          <t>maine</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 20, 'name': 'Maine', 'label': 'Maine'}</t>
+          <t>Maine</t>
         </is>
       </c>
     </row>
@@ -1545,12 +1545,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_21,_'name':_'maryland',_'label':_'maryland'}</t>
+          <t>maryland</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 21, 'name': 'Maryland', 'label': 'Maryland'}</t>
+          <t>Maryland</t>
         </is>
       </c>
     </row>
@@ -1562,12 +1562,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_22,_'name':_'massachusetts',_'label':_'massachusetts'}</t>
+          <t>massachusetts</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 22, 'name': 'Massachusetts', 'label': 'Massachusetts'}</t>
+          <t>Massachusetts</t>
         </is>
       </c>
     </row>
@@ -1579,12 +1579,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_23,_'name':_'michigan',_'label':_'michigan'}</t>
+          <t>michigan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 23, 'name': 'Michigan', 'label': 'Michigan'}</t>
+          <t>Michigan</t>
         </is>
       </c>
     </row>
@@ -1596,12 +1596,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_24,_'name':_'minnesota',_'label':_'minnesota'}</t>
+          <t>minnesota</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 24, 'name': 'Minnesota', 'label': 'Minnesota'}</t>
+          <t>Minnesota</t>
         </is>
       </c>
     </row>
@@ -1613,12 +1613,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_25,_'name':_'mississippi',_'label':_'mississippi'}</t>
+          <t>mississippi</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 25, 'name': 'Mississippi', 'label': 'Mississippi'}</t>
+          <t>Mississippi</t>
         </is>
       </c>
     </row>
